--- a/data/trans_camb/P44D-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P44D-Habitat-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-4,37</t>
+          <t>-4,24</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,4</t>
+          <t>-2,54</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,36</t>
+          <t>-3,37</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,5; 0,0</t>
+          <t>-32,16; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 2,86</t>
+          <t>-27,93; 3,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,26; 0,0</t>
+          <t>-30,79; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 4,5</t>
+          <t>-22,91; 4,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 0,0</t>
+          <t>-18,95; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 2,78</t>
+          <t>-20,65; 2,68</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-69,69%</t>
+          <t>-67,69%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-39,44%</t>
+          <t>-41,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-54,4%</t>
+          <t>-54,64%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-91,62; —</t>
+          <t>-92,3; —</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-9,81</t>
+          <t>-5,39</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-7,09</t>
+          <t>-7,22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-9,2</t>
+          <t>-6,28</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,09; 19,09</t>
+          <t>-22,4; 21,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-37,64; 1,8</t>
+          <t>-34,33; 6,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 22,66</t>
+          <t>-13,19; 22,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 1,58</t>
+          <t>-21,42; 1,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 16,69</t>
+          <t>-10,35; 16,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,0; -1,11</t>
+          <t>-17,73; 2,17</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-80,22%</t>
+          <t>-44,09%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-57,07%</t>
+          <t>-58,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-74,55%</t>
+          <t>-50,87%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-88,62; —</t>
+          <t>-84,35; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-98,54; inf</t>
+          <t>-90,47; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-82,98; 483,17</t>
+          <t>-77,34; 630,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-85,02; 54,99</t>
+          <t>-85,54; 50,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,04; 294,65</t>
+          <t>-54,95; 290,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-94,92; -25,72</t>
+          <t>-79,54; 52,0</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7,75</t>
+          <t>7,89</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-13,45</t>
+          <t>-13,03</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,4</t>
+          <t>-2,18</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 17,82</t>
+          <t>-11,33; 20,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 17,99</t>
+          <t>-6,41; 17,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-33,63; 15,53</t>
+          <t>-33,21; 19,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-38,4; 4,62</t>
+          <t>-37,47; 4,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 10,22</t>
+          <t>-20,49; 11,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 8,2</t>
+          <t>-17,66; 7,86</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>106,2%</t>
+          <t>108,22%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-51,76%</t>
+          <t>-50,15%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-14,61%</t>
+          <t>-13,26%</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,25; —</t>
+          <t>-52,84; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 134,59</t>
+          <t>-100,0; 231,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-81,34; 55,63</t>
+          <t>-79,58; 45,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,1; 121,88</t>
+          <t>-80,55; 167,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-59,1; 132,19</t>
+          <t>-58,01; 110,09</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-7,27</t>
+          <t>-7,2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-15,15</t>
+          <t>-15,56</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-10,85</t>
+          <t>-11,07</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 20,48</t>
+          <t>-17,46; 20,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 5,64</t>
+          <t>-25,87; 6,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 9,21</t>
+          <t>-32,26; 10,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-38,96; 0,16</t>
+          <t>-36,49; 0,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 11,22</t>
+          <t>-18,76; 10,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,07; -0,84</t>
+          <t>-24,24; -0,61</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-36,14%</t>
+          <t>-35,76%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-63,56%</t>
+          <t>-65,29%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-50,08%</t>
+          <t>-51,08%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-53,36; 221,31</t>
+          <t>-57,38; 248,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-73,18; 62,38</t>
+          <t>-70,92; 81,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-91,9; 124,74</t>
+          <t>-91,97; 155,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-84,55; 0,91</t>
+          <t>-85,3; 12,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-54,91; 83,97</t>
+          <t>-57,41; 80,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-72,35; -4,12</t>
+          <t>-72,34; -6,13</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-6,33</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-10,56</t>
+          <t>-10,65</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-8,49</t>
+          <t>-6,82</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 9,68</t>
+          <t>-9,35; 9,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 0,1</t>
+          <t>-12,63; 3,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 3,3</t>
+          <t>-17,08; 3,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -3,74</t>
+          <t>-19,65; -3,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 4,57</t>
+          <t>-9,59; 4,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,34; -2,63</t>
+          <t>-13,36; -1,36</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-48,73%</t>
+          <t>-24,45%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-58,93%</t>
+          <t>-59,45%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-55,06%</t>
+          <t>-44,26%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-48,54; 125,34</t>
+          <t>-52,31; 128,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-82,34; 0,04</t>
+          <t>-59,15; 54,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-73,88; 30,35</t>
+          <t>-71,51; 36,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-74,87; -31,79</t>
+          <t>-74,08; -26,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 39,88</t>
+          <t>-48,34; 45,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-76,61; -28,23</t>
+          <t>-61,48; -12,38</t>
         </is>
       </c>
     </row>
